--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -470,7 +470,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -493,7 +493,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -493,7 +493,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,163 +455,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>AR-F5203</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>120</v>
-      </c>
-      <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1030-1060-1104-1122-4.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>AR-F5103A</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>18</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1042-1082-1108-1131-4.5</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AR-F5103</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>120</v>
-      </c>
-      <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>38" x 150#</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>AR-F5106 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>12"X300#</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>HP-F8701 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>12</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>12"X300#</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>7블럭</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>HP-F8703 (12"x300#)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>7</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>12"X300#</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>10블럭</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>TG-F7103</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>10</v>
-      </c>
-      <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,163 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AR-F5203</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>120</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1030-1060-1104-1122-4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AR-F5103A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1042-1082-1108-1131-4.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AR-F5103</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>120</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>38" x 150#</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AR-F5106 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>12"X300#</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>HP-F8701 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>12"X300#</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>7블럭</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>HP-F8703 (12"x300#)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12"X300#</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>10블럭</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TG-F7103</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -470,7 +470,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -470,7 +470,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -470,7 +470,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -493,7 +493,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -470,7 +470,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/filter_master_HOU.xlsx
+++ b/filter_master_HOU.xlsx
@@ -516,7 +516,7 @@
         <v>120</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
